--- a/output/pdf_financials_xlsx/DND.xlsx
+++ b/output/pdf_financials_xlsx/DND.xlsx
@@ -9998,7 +9998,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">

--- a/output/pdf_financials_xlsx/DND.xlsx
+++ b/output/pdf_financials_xlsx/DND.xlsx
@@ -13510,7 +13510,11 @@
           <t>Additions to intangible assets 10</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DND.xlsx
+++ b/output/pdf_financials_xlsx/DND.xlsx
@@ -823,7 +823,7 @@
         <v>-193.85</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-174.348</v>
+        <v>-140.771</v>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
@@ -844,16 +844,16 @@
         <v>1.254</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-10.246</v>
+        <v>10.246</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>23.207</v>
+        <v>-23.207</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-33.577</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-31.809</v>
       </c>
     </row>
     <row r="18">
@@ -1146,7 +1146,7 @@
         <v>-193.85</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-174.348</v>
+        <v>-140.771</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>-193.85</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-174.348</v>
+        <v>-140.771</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>-42.97225701333392</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-38.09244980849776</v>
+        <v>-30.756373758185</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>-11.97162754707248</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0</v>
+        <v>-23.85221387927911</v>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
@@ -17052,7 +17052,11 @@
           <t>Income tax recovery 21 19,352</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -18084,7 +18088,11 @@
           <t>Income tax recovery 21</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -18664,7 +18672,11 @@
           <t>Income tax recovery (expense) 21</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
